--- a/experiment_results/combined_sweep/rtt_bursts_S2_atk5pct_wu300000.xlsx
+++ b/experiment_results/combined_sweep/rtt_bursts_S2_atk5pct_wu300000.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -605,12 +605,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>38142</t>
+          <t>18157</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>25379</t>
+          <t>8190</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -776,12 +776,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>7027</t>
+          <t>524</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>15591</t>
+          <t>8472</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -947,12 +947,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>9015</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>170404</t>
+          <t>84719</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1175,12 +1175,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>168500</t>
+          <t>84533</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>185402</t>
+          <t>101622</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>194169</t>
+          <t>93300</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>171974</t>
+          <t>79427</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>146266</t>
+          <t>67591</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1460,12 +1460,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>134430</t>
+          <t>67591</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
